--- a/output/yearly_total_coral_cover_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_23_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.261758284733167</v>
+        <v>1.269563178981929</v>
       </c>
       <c r="C3" t="n">
-        <v>4.589981622436246</v>
+        <v>4.66195354663458</v>
       </c>
       <c r="D3" t="n">
-        <v>6.118394140217878</v>
+        <v>6.144390819426333</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97013404738729</v>
+        <v>12.07590754504284</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.394575418910541</v>
+        <v>1.414859836995135</v>
       </c>
       <c r="C4" t="n">
-        <v>5.016520229374184</v>
+        <v>5.20709056424587</v>
       </c>
       <c r="D4" t="n">
-        <v>6.371194698879404</v>
+        <v>6.450075994628667</v>
       </c>
       <c r="E4" t="n">
-        <v>12.78229034716413</v>
+        <v>13.07202639586967</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.581279846308841</v>
+        <v>1.62043471199873</v>
       </c>
       <c r="C5" t="n">
-        <v>5.532854814256104</v>
+        <v>5.897062997900293</v>
       </c>
       <c r="D5" t="n">
-        <v>6.665944642969966</v>
+        <v>6.800555753532948</v>
       </c>
       <c r="E5" t="n">
-        <v>13.78007930353491</v>
+        <v>14.31805346343197</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.789086144920456</v>
+        <v>1.847734877081696</v>
       </c>
       <c r="C6" t="n">
-        <v>6.149305271850216</v>
+        <v>6.735433743752557</v>
       </c>
       <c r="D6" t="n">
-        <v>7.061314075400676</v>
+        <v>7.154910335679673</v>
       </c>
       <c r="E6" t="n">
-        <v>14.99970549217135</v>
+        <v>15.73807895651393</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.017925873082655</v>
+        <v>2.118607328768104</v>
       </c>
       <c r="C7" t="n">
-        <v>6.866553396646744</v>
+        <v>7.742942767685311</v>
       </c>
       <c r="D7" t="n">
-        <v>7.472857793777766</v>
+        <v>7.661524953353129</v>
       </c>
       <c r="E7" t="n">
-        <v>16.35733706350716</v>
+        <v>17.52307504980654</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.223931716404445</v>
+        <v>1.338847756243229</v>
       </c>
       <c r="C8" t="n">
-        <v>4.479913859660085</v>
+        <v>5.38395527170505</v>
       </c>
       <c r="D8" t="n">
-        <v>5.680873230764127</v>
+        <v>5.971116628214205</v>
       </c>
       <c r="E8" t="n">
-        <v>11.38471880682866</v>
+        <v>12.69391965616249</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.525057388651658</v>
+        <v>1.687434088340521</v>
       </c>
       <c r="C9" t="n">
-        <v>5.371584644077771</v>
+        <v>6.617142571745001</v>
       </c>
       <c r="D9" t="n">
-        <v>6.154597821534887</v>
+        <v>6.528197319331508</v>
       </c>
       <c r="E9" t="n">
-        <v>13.05123985426432</v>
+        <v>14.83277397941703</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.856555478233585</v>
+        <v>2.05705853228012</v>
       </c>
       <c r="C10" t="n">
-        <v>6.428182691126842</v>
+        <v>7.985262824107012</v>
       </c>
       <c r="D10" t="n">
-        <v>6.623087844507486</v>
+        <v>7.083467785214092</v>
       </c>
       <c r="E10" t="n">
-        <v>14.90782601386791</v>
+        <v>17.12578914160122</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.207540508700287</v>
+        <v>2.425031484639625</v>
       </c>
       <c r="C11" t="n">
-        <v>7.631315092044081</v>
+        <v>9.431553040620965</v>
       </c>
       <c r="D11" t="n">
-        <v>7.171835187318661</v>
+        <v>7.593314646445405</v>
       </c>
       <c r="E11" t="n">
-        <v>17.01069078806303</v>
+        <v>19.44989917170599</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.585325564753553</v>
+        <v>2.789958069804529</v>
       </c>
       <c r="C12" t="n">
-        <v>8.942174912995046</v>
+        <v>10.97919373784816</v>
       </c>
       <c r="D12" t="n">
-        <v>7.675488851829916</v>
+        <v>8.207721479959481</v>
       </c>
       <c r="E12" t="n">
-        <v>19.20298932957851</v>
+        <v>21.97687328761217</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.973116568889191</v>
+        <v>3.12578905497157</v>
       </c>
       <c r="C13" t="n">
-        <v>10.32140183503271</v>
+        <v>12.55821221193926</v>
       </c>
       <c r="D13" t="n">
-        <v>8.106666111478166</v>
+        <v>8.752580936316036</v>
       </c>
       <c r="E13" t="n">
-        <v>21.40118451540006</v>
+        <v>24.43658220322686</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.745105631683918</v>
+        <v>1.790236573648144</v>
       </c>
       <c r="C14" t="n">
-        <v>7.328962596697373</v>
+        <v>8.819324334083328</v>
       </c>
       <c r="D14" t="n">
-        <v>6.148401164863541</v>
+        <v>6.630125128383367</v>
       </c>
       <c r="E14" t="n">
-        <v>15.22246939324483</v>
+        <v>17.23968603611484</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.825392958937222</v>
+        <v>1.829369037139422</v>
       </c>
       <c r="C15" t="n">
-        <v>7.882982461157934</v>
+        <v>9.508491587510505</v>
       </c>
       <c r="D15" t="n">
-        <v>6.15399712677775</v>
+        <v>6.686359636882624</v>
       </c>
       <c r="E15" t="n">
-        <v>15.8623725468729</v>
+        <v>18.02422026153255</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.164203909149839</v>
+        <v>2.110963731148534</v>
       </c>
       <c r="C16" t="n">
-        <v>9.337461319953668</v>
+        <v>11.18391276714699</v>
       </c>
       <c r="D16" t="n">
-        <v>6.629850239026177</v>
+        <v>7.172413107778177</v>
       </c>
       <c r="E16" t="n">
-        <v>18.13151546812968</v>
+        <v>20.4672896060737</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.762649463158808</v>
+        <v>1.686328396630661</v>
       </c>
       <c r="C17" t="n">
-        <v>8.669166022718779</v>
+        <v>10.22830900426427</v>
       </c>
       <c r="D17" t="n">
-        <v>6.151523122563047</v>
+        <v>6.691111295771178</v>
       </c>
       <c r="E17" t="n">
-        <v>16.58333860844063</v>
+        <v>18.60574869666611</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.049840119082128</v>
+        <v>1.916086811855542</v>
       </c>
       <c r="C18" t="n">
-        <v>10.1167530126307</v>
+        <v>11.8599344188143</v>
       </c>
       <c r="D18" t="n">
-        <v>6.575019629743994</v>
+        <v>7.210956522646907</v>
       </c>
       <c r="E18" t="n">
-        <v>18.74161276145682</v>
+        <v>20.98697775331675</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.095756459209751</v>
+        <v>1.913818974658732</v>
       </c>
       <c r="C19" t="n">
-        <v>10.83536287970824</v>
+        <v>12.62086742942192</v>
       </c>
       <c r="D19" t="n">
-        <v>6.68562332610444</v>
+        <v>7.336816578331348</v>
       </c>
       <c r="E19" t="n">
-        <v>19.61674266502243</v>
+        <v>21.871502982412</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.381248691604724</v>
+        <v>2.119446031313227</v>
       </c>
       <c r="C20" t="n">
-        <v>12.53200944471053</v>
+        <v>14.44647637285407</v>
       </c>
       <c r="D20" t="n">
-        <v>7.111839274426149</v>
+        <v>7.860048834786729</v>
       </c>
       <c r="E20" t="n">
-        <v>22.02509741074141</v>
+        <v>24.42597123895403</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.445181708036517</v>
+        <v>1.252572625940336</v>
       </c>
       <c r="C21" t="n">
-        <v>9.266618405615219</v>
+        <v>10.57909727646869</v>
       </c>
       <c r="D21" t="n">
-        <v>5.917111223220036</v>
+        <v>6.594242249793146</v>
       </c>
       <c r="E21" t="n">
-        <v>16.62891133687177</v>
+        <v>18.42591215220218</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_23_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.269563178981929</v>
+        <v>1.270927808290832</v>
       </c>
       <c r="C3" t="n">
-        <v>4.66195354663458</v>
+        <v>4.629987841384303</v>
       </c>
       <c r="D3" t="n">
-        <v>6.144390819426333</v>
+        <v>6.137754204945625</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07590754504284</v>
+        <v>12.03866985462076</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.414859836995135</v>
+        <v>1.419225168191986</v>
       </c>
       <c r="C4" t="n">
-        <v>5.20709056424587</v>
+        <v>5.167755837406134</v>
       </c>
       <c r="D4" t="n">
-        <v>6.450075994628667</v>
+        <v>6.415882471665044</v>
       </c>
       <c r="E4" t="n">
-        <v>13.07202639586967</v>
+        <v>13.00286347726316</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.62043471199873</v>
+        <v>1.613415953130761</v>
       </c>
       <c r="C5" t="n">
-        <v>5.897062997900293</v>
+        <v>5.890952372727838</v>
       </c>
       <c r="D5" t="n">
-        <v>6.800555753532948</v>
+        <v>6.751865356280512</v>
       </c>
       <c r="E5" t="n">
-        <v>14.31805346343197</v>
+        <v>14.25623368213911</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.847734877081696</v>
+        <v>1.835497018700078</v>
       </c>
       <c r="C6" t="n">
-        <v>6.735433743752557</v>
+        <v>6.80494264051629</v>
       </c>
       <c r="D6" t="n">
-        <v>7.154910335679673</v>
+        <v>7.11646377508469</v>
       </c>
       <c r="E6" t="n">
-        <v>15.73807895651393</v>
+        <v>15.75690343430106</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.118607328768104</v>
+        <v>2.079340645608645</v>
       </c>
       <c r="C7" t="n">
-        <v>7.742942767685311</v>
+        <v>7.884557070932313</v>
       </c>
       <c r="D7" t="n">
-        <v>7.661524953353129</v>
+        <v>7.545002393339545</v>
       </c>
       <c r="E7" t="n">
-        <v>17.52307504980654</v>
+        <v>17.5089001098805</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.338847756243229</v>
+        <v>1.277354986990862</v>
       </c>
       <c r="C8" t="n">
-        <v>5.38395527170505</v>
+        <v>5.571725376843017</v>
       </c>
       <c r="D8" t="n">
-        <v>5.971116628214205</v>
+        <v>5.73675257654105</v>
       </c>
       <c r="E8" t="n">
-        <v>12.69391965616249</v>
+        <v>12.58583294037493</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.687434088340521</v>
+        <v>1.594888736215453</v>
       </c>
       <c r="C9" t="n">
-        <v>6.617142571745001</v>
+        <v>6.905383514460085</v>
       </c>
       <c r="D9" t="n">
-        <v>6.528197319331508</v>
+        <v>6.310198335830693</v>
       </c>
       <c r="E9" t="n">
-        <v>14.83277397941703</v>
+        <v>14.81047058650623</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.05705853228012</v>
+        <v>1.923370477813992</v>
       </c>
       <c r="C10" t="n">
-        <v>7.985262824107012</v>
+        <v>8.394453050014031</v>
       </c>
       <c r="D10" t="n">
-        <v>7.083467785214092</v>
+        <v>6.858140152177032</v>
       </c>
       <c r="E10" t="n">
-        <v>17.12578914160122</v>
+        <v>17.17596368000505</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.425031484639625</v>
+        <v>2.24980214684301</v>
       </c>
       <c r="C11" t="n">
-        <v>9.431553040620965</v>
+        <v>10.0498844521024</v>
       </c>
       <c r="D11" t="n">
-        <v>7.593314646445405</v>
+        <v>7.390193856371138</v>
       </c>
       <c r="E11" t="n">
-        <v>19.44989917170599</v>
+        <v>19.68988045531655</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.789958069804529</v>
+        <v>2.563031687019206</v>
       </c>
       <c r="C12" t="n">
-        <v>10.97919373784816</v>
+        <v>11.84028495716662</v>
       </c>
       <c r="D12" t="n">
-        <v>8.207721479959481</v>
+        <v>7.969004882127569</v>
       </c>
       <c r="E12" t="n">
-        <v>21.97687328761217</v>
+        <v>22.37232152631339</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.12578905497157</v>
+        <v>2.858042532792225</v>
       </c>
       <c r="C13" t="n">
-        <v>12.55821221193926</v>
+        <v>13.63478794005993</v>
       </c>
       <c r="D13" t="n">
-        <v>8.752580936316036</v>
+        <v>8.443703021997983</v>
       </c>
       <c r="E13" t="n">
-        <v>24.43658220322686</v>
+        <v>24.93653349485014</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.790236573648144</v>
+        <v>1.643818721036775</v>
       </c>
       <c r="C14" t="n">
-        <v>8.819324334083328</v>
+        <v>9.559699547764019</v>
       </c>
       <c r="D14" t="n">
-        <v>6.630125128383367</v>
+        <v>6.413306147900458</v>
       </c>
       <c r="E14" t="n">
-        <v>17.23968603611484</v>
+        <v>17.61682441670125</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.829369037139422</v>
+        <v>1.663915096542707</v>
       </c>
       <c r="C15" t="n">
-        <v>9.508491587510505</v>
+        <v>10.45185295652126</v>
       </c>
       <c r="D15" t="n">
-        <v>6.686359636882624</v>
+        <v>6.437516046287185</v>
       </c>
       <c r="E15" t="n">
-        <v>18.02422026153255</v>
+        <v>18.55328409935116</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.110963731148534</v>
+        <v>1.906387144537584</v>
       </c>
       <c r="C16" t="n">
-        <v>11.18391276714699</v>
+        <v>12.44377977852987</v>
       </c>
       <c r="D16" t="n">
-        <v>7.172413107778177</v>
+        <v>6.897720100129921</v>
       </c>
       <c r="E16" t="n">
-        <v>20.4672896060737</v>
+        <v>21.24788702319738</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.686328396630661</v>
+        <v>1.511783472292621</v>
       </c>
       <c r="C17" t="n">
-        <v>10.22830900426427</v>
+        <v>11.53057769899358</v>
       </c>
       <c r="D17" t="n">
-        <v>6.691111295771178</v>
+        <v>6.381134275632291</v>
       </c>
       <c r="E17" t="n">
-        <v>18.60574869666611</v>
+        <v>19.42349544691849</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.916086811855542</v>
+        <v>1.6983351710536</v>
       </c>
       <c r="C18" t="n">
-        <v>11.8599344188143</v>
+        <v>13.48374512163852</v>
       </c>
       <c r="D18" t="n">
-        <v>7.210956522646907</v>
+        <v>6.785329622947745</v>
       </c>
       <c r="E18" t="n">
-        <v>20.98697775331675</v>
+        <v>21.96740991563987</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.913818974658732</v>
+        <v>1.67908309857332</v>
       </c>
       <c r="C19" t="n">
-        <v>12.62086742942192</v>
+        <v>14.43597167241863</v>
       </c>
       <c r="D19" t="n">
-        <v>7.336816578331348</v>
+        <v>6.868778177808724</v>
       </c>
       <c r="E19" t="n">
-        <v>21.871502982412</v>
+        <v>22.98383294880067</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.119446031313227</v>
+        <v>1.838224401431728</v>
       </c>
       <c r="C20" t="n">
-        <v>14.44647637285407</v>
+        <v>16.4937737653822</v>
       </c>
       <c r="D20" t="n">
-        <v>7.860048834786729</v>
+        <v>7.246122725413028</v>
       </c>
       <c r="E20" t="n">
-        <v>24.42597123895403</v>
+        <v>25.57812089222695</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.252572625940336</v>
+        <v>1.076545262568882</v>
       </c>
       <c r="C21" t="n">
-        <v>10.57909727646869</v>
+        <v>12.03826888929073</v>
       </c>
       <c r="D21" t="n">
-        <v>6.594242249793146</v>
+        <v>6.032113149295506</v>
       </c>
       <c r="E21" t="n">
-        <v>18.42591215220218</v>
+        <v>19.14692730115512</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_23_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.270927808290832</v>
+        <v>2.601729112908002</v>
       </c>
       <c r="C3" t="n">
-        <v>4.629987841384303</v>
+        <v>7.685559984667449</v>
       </c>
       <c r="D3" t="n">
-        <v>6.137754204945625</v>
+        <v>8.259912479783875</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03866985462076</v>
+        <v>18.54720157735932</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.419225168191986</v>
+        <v>1.096646213742793</v>
       </c>
       <c r="C4" t="n">
-        <v>5.167755837406134</v>
+        <v>4.465707779216526</v>
       </c>
       <c r="D4" t="n">
-        <v>6.415882471665044</v>
+        <v>5.826574100480457</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00286347726316</v>
+        <v>11.38892809343978</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.613415953130761</v>
+        <v>1.213048669008736</v>
       </c>
       <c r="C5" t="n">
-        <v>5.890952372727838</v>
+        <v>5.09276094807228</v>
       </c>
       <c r="D5" t="n">
-        <v>6.751865356280512</v>
+        <v>6.119175255046925</v>
       </c>
       <c r="E5" t="n">
-        <v>14.25623368213911</v>
+        <v>12.42498487212794</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.835497018700078</v>
+        <v>1.336884964574095</v>
       </c>
       <c r="C6" t="n">
-        <v>6.80494264051629</v>
+        <v>5.886594323972067</v>
       </c>
       <c r="D6" t="n">
-        <v>7.11646377508469</v>
+        <v>6.415819396322171</v>
       </c>
       <c r="E6" t="n">
-        <v>15.75690343430106</v>
+        <v>13.63929868486833</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.079340645608645</v>
+        <v>1.459317795572713</v>
       </c>
       <c r="C7" t="n">
-        <v>7.884557070932313</v>
+        <v>6.842440370377034</v>
       </c>
       <c r="D7" t="n">
-        <v>7.545002393339545</v>
+        <v>6.839636061738303</v>
       </c>
       <c r="E7" t="n">
-        <v>17.5089001098805</v>
+        <v>15.14139422768805</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.277354986990862</v>
+        <v>1.591856163447051</v>
       </c>
       <c r="C8" t="n">
-        <v>5.571725376843017</v>
+        <v>7.906829243998552</v>
       </c>
       <c r="D8" t="n">
-        <v>5.73675257654105</v>
+        <v>7.224146640152479</v>
       </c>
       <c r="E8" t="n">
-        <v>12.58583294037493</v>
+        <v>16.72283204759808</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.594888736215453</v>
+        <v>1.72700312177253</v>
       </c>
       <c r="C9" t="n">
-        <v>6.905383514460085</v>
+        <v>9.09313543068793</v>
       </c>
       <c r="D9" t="n">
-        <v>6.310198335830693</v>
+        <v>7.70714609955614</v>
       </c>
       <c r="E9" t="n">
-        <v>14.81047058650623</v>
+        <v>18.5272846520166</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.923370477813992</v>
+        <v>1.081306738934479</v>
       </c>
       <c r="C10" t="n">
-        <v>8.394453050014031</v>
+        <v>6.705454629730224</v>
       </c>
       <c r="D10" t="n">
-        <v>6.858140152177032</v>
+        <v>6.073346552873874</v>
       </c>
       <c r="E10" t="n">
-        <v>17.17596368000505</v>
+        <v>13.86010792153858</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.24980214684301</v>
+        <v>1.018671235403533</v>
       </c>
       <c r="C11" t="n">
-        <v>10.0498844521024</v>
+        <v>7.072971882815018</v>
       </c>
       <c r="D11" t="n">
-        <v>7.390193856371138</v>
+        <v>5.95646948868329</v>
       </c>
       <c r="E11" t="n">
-        <v>19.68988045531655</v>
+        <v>14.04811260690184</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.563031687019206</v>
+        <v>1.107558672546039</v>
       </c>
       <c r="C12" t="n">
-        <v>11.84028495716662</v>
+        <v>8.365678354904963</v>
       </c>
       <c r="D12" t="n">
-        <v>7.969004882127569</v>
+        <v>6.332292327346011</v>
       </c>
       <c r="E12" t="n">
-        <v>22.37232152631339</v>
+        <v>15.80552935479701</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.858042532792225</v>
+        <v>0.8793612361709106</v>
       </c>
       <c r="C13" t="n">
-        <v>13.63478794005993</v>
+        <v>8.005249320244831</v>
       </c>
       <c r="D13" t="n">
-        <v>8.443703021997983</v>
+        <v>5.798545552978148</v>
       </c>
       <c r="E13" t="n">
-        <v>24.93653349485014</v>
+        <v>14.68315610939389</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.643818721036775</v>
+        <v>0.9622011074552566</v>
       </c>
       <c r="C14" t="n">
-        <v>9.559699547764019</v>
+        <v>9.416766899502726</v>
       </c>
       <c r="D14" t="n">
-        <v>6.413306147900458</v>
+        <v>6.160211589745631</v>
       </c>
       <c r="E14" t="n">
-        <v>17.61682441670125</v>
+        <v>16.53917959670361</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.663915096542707</v>
+        <v>0.9374316128771095</v>
       </c>
       <c r="C15" t="n">
-        <v>10.45185295652126</v>
+        <v>10.20194907840524</v>
       </c>
       <c r="D15" t="n">
-        <v>6.437516046287185</v>
+        <v>6.220697065804277</v>
       </c>
       <c r="E15" t="n">
-        <v>18.55328409935116</v>
+        <v>17.36007775708662</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.906387144537584</v>
+        <v>1.034614818120501</v>
       </c>
       <c r="C16" t="n">
-        <v>12.44377977852987</v>
+        <v>11.93145473906868</v>
       </c>
       <c r="D16" t="n">
-        <v>6.897720100129921</v>
+        <v>6.670828388201439</v>
       </c>
       <c r="E16" t="n">
-        <v>21.24788702319738</v>
+        <v>19.63689794539062</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.511783472292621</v>
+        <v>0.6282694433327464</v>
       </c>
       <c r="C17" t="n">
-        <v>11.53057769899358</v>
+        <v>8.97385142273178</v>
       </c>
       <c r="D17" t="n">
-        <v>6.381134275632291</v>
+        <v>5.562179975703687</v>
       </c>
       <c r="E17" t="n">
-        <v>19.42349544691849</v>
+        <v>15.16430084176821</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.6983351710536</v>
+        <v>0.500475344670939</v>
       </c>
       <c r="C18" t="n">
-        <v>13.48374512163852</v>
+        <v>7.965184196434519</v>
       </c>
       <c r="D18" t="n">
-        <v>6.785329622947745</v>
+        <v>5.083146000893499</v>
       </c>
       <c r="E18" t="n">
-        <v>21.96740991563987</v>
+        <v>13.54880554199896</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.67908309857332</v>
+        <v>0.5899812828671207</v>
       </c>
       <c r="C19" t="n">
-        <v>14.43597167241863</v>
+        <v>9.83667021008613</v>
       </c>
       <c r="D19" t="n">
-        <v>6.868778177808724</v>
+        <v>5.583032296941888</v>
       </c>
       <c r="E19" t="n">
-        <v>22.98383294880067</v>
+        <v>16.00968378989514</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.838224401431728</v>
+        <v>0.6711129131460771</v>
       </c>
       <c r="C20" t="n">
-        <v>16.4937737653822</v>
+        <v>11.90545805986022</v>
       </c>
       <c r="D20" t="n">
-        <v>7.246122725413028</v>
+        <v>6.087257917843051</v>
       </c>
       <c r="E20" t="n">
-        <v>25.57812089222695</v>
+        <v>18.66382889084935</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.076545262568882</v>
+        <v>0.7441254899109124</v>
       </c>
       <c r="C21" t="n">
-        <v>12.03826888929073</v>
+        <v>14.02014261480785</v>
       </c>
       <c r="D21" t="n">
-        <v>6.032113149295506</v>
+        <v>6.559400023769427</v>
       </c>
       <c r="E21" t="n">
-        <v>19.14692730115512</v>
+        <v>21.32366812848819</v>
       </c>
     </row>
   </sheetData>
